--- a/Result/profitability/1512.xlsx
+++ b/Result/profitability/1512.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04125</v>
+        <v>-0.03000000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>27.65625</v>
+        <v>29.2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01375</v>
+        <v>0.02</v>
       </c>
       <c r="N3" t="n">
-        <v>26.6525</v>
+        <v>28.335</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04625</v>
+        <v>0.0375</v>
       </c>
       <c r="N4" t="n">
-        <v>25.76375</v>
+        <v>26.60875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0075</v>
+        <v>-0.003750000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>23.015</v>
+        <v>22.9275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02375</v>
+        <v>-0.035</v>
       </c>
       <c r="N6" t="n">
-        <v>19.46875</v>
+        <v>19.43125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06</v>
+        <v>-0.08750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>16.69</v>
+        <v>17.5775</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0575</v>
+        <v>-0.0775</v>
       </c>
       <c r="N8" t="n">
-        <v>15.54625</v>
+        <v>16.0125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.02</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06624999999999999</v>
+        <v>-0.06625</v>
       </c>
       <c r="N9" t="n">
         <v>13.535</v>
@@ -1899,7 +1899,7 @@
         <v>0.82</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.006250000000000006</v>
+        <v>-0.006250000000000019</v>
       </c>
       <c r="N12" t="n">
         <v>12.93375</v>
@@ -2026,7 +2026,7 @@
         <v>0.15</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05125</v>
+        <v>0.05124999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>14.2175</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>231</v>
+      </c>
+      <c r="D75" t="n">
+        <v>149</v>
+      </c>
+      <c r="E75" t="n">
+        <v>82</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.777777777777778</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1172955974842766</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.09000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.6999999999999957</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01932100469224385</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
